--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/96.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/96.xlsx
@@ -426,13 +426,13 @@
         <v>-16.8870282656651</v>
       </c>
       <c r="E2">
-        <v>-12.09353645178771</v>
+        <v>-10.99389616545313</v>
       </c>
       <c r="F2">
-        <v>0.3667278397205331</v>
+        <v>0.1969727782034519</v>
       </c>
       <c r="G2">
-        <v>-14.02478303105463</v>
+        <v>-14.69786494209879</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-15.57294082837053</v>
       </c>
       <c r="E3">
-        <v>-12.74720356089889</v>
+        <v>-11.25380793112337</v>
       </c>
       <c r="F3">
-        <v>0.5886018710617689</v>
+        <v>0.609807693269503</v>
       </c>
       <c r="G3">
-        <v>-13.40738615125379</v>
+        <v>-13.33996689134653</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-14.03686087405346</v>
       </c>
       <c r="E4">
-        <v>-13.52161337247659</v>
+        <v>-12.49841372739149</v>
       </c>
       <c r="F4">
-        <v>0.2939739736711603</v>
+        <v>0.4411738955405529</v>
       </c>
       <c r="G4">
-        <v>-12.74742558745454</v>
+        <v>-12.97327431468916</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-12.50687584637621</v>
       </c>
       <c r="E5">
-        <v>-14.27215359755986</v>
+        <v>-13.02803687648457</v>
       </c>
       <c r="F5">
-        <v>0.2667492771317985</v>
+        <v>0.5126473353572929</v>
       </c>
       <c r="G5">
-        <v>-11.89981337085278</v>
+        <v>-11.94178446719966</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-10.99834536215735</v>
       </c>
       <c r="E6">
-        <v>-15.53136825097673</v>
+        <v>-14.36229287268254</v>
       </c>
       <c r="F6">
-        <v>0.4923632299923445</v>
+        <v>0.4001487856540518</v>
       </c>
       <c r="G6">
-        <v>-11.761664305499</v>
+        <v>-10.14638623652334</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-9.563825773086121</v>
       </c>
       <c r="E7">
-        <v>-14.77049857668196</v>
+        <v>-13.42054688957341</v>
       </c>
       <c r="F7">
-        <v>0.6985126452991819</v>
+        <v>0.771768546123749</v>
       </c>
       <c r="G7">
-        <v>-11.22307496226051</v>
+        <v>-11.19719311723448</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-8.190229168561594</v>
       </c>
       <c r="E8">
-        <v>-16.5445146837648</v>
+        <v>-16.11688635474648</v>
       </c>
       <c r="F8">
-        <v>0.5907572948126819</v>
+        <v>0.5720917368933126</v>
       </c>
       <c r="G8">
-        <v>-10.13170396705667</v>
+        <v>-9.418910406996192</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.864560036400099</v>
       </c>
       <c r="E9">
-        <v>-16.51370294661661</v>
+        <v>-15.92275067403765</v>
       </c>
       <c r="F9">
-        <v>0.5845507513300747</v>
+        <v>0.9720059872482509</v>
       </c>
       <c r="G9">
-        <v>-9.689216450277684</v>
+        <v>-8.429490972219751</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.557955835430652</v>
       </c>
       <c r="E10">
-        <v>-17.41419000304186</v>
+        <v>-15.66057014288957</v>
       </c>
       <c r="F10">
-        <v>0.5397152450110262</v>
+        <v>0.1436929519432803</v>
       </c>
       <c r="G10">
-        <v>-8.837509088843847</v>
+        <v>-7.618486768191253</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.250397231076671</v>
       </c>
       <c r="E11">
-        <v>-18.40300947346073</v>
+        <v>-17.87894276197506</v>
       </c>
       <c r="F11">
-        <v>0.583877676316013</v>
+        <v>0.4394698279755401</v>
       </c>
       <c r="G11">
-        <v>-7.499274023322097</v>
+        <v>-7.696827517832566</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-2.929100459254702</v>
       </c>
       <c r="E12">
-        <v>-18.78326996435882</v>
+        <v>-17.66605014192647</v>
       </c>
       <c r="F12">
-        <v>0.6517378910866778</v>
+        <v>0.658387872225608</v>
       </c>
       <c r="G12">
-        <v>-7.72143149228043</v>
+        <v>-5.548227183571398</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-1.594264661444075</v>
       </c>
       <c r="E13">
-        <v>-19.53784505978292</v>
+        <v>-19.05510520209126</v>
       </c>
       <c r="F13">
-        <v>0.8409939153935226</v>
+        <v>0.7047635325474214</v>
       </c>
       <c r="G13">
-        <v>-6.132657650892177</v>
+        <v>-5.377836715210649</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-0.2669410013711492</v>
       </c>
       <c r="E14">
-        <v>-20.64703136932567</v>
+        <v>-19.29867823354182</v>
       </c>
       <c r="F14">
-        <v>0.6855626820286336</v>
+        <v>0.5321292936760713</v>
       </c>
       <c r="G14">
-        <v>-5.702909113348305</v>
+        <v>-4.244027836738896</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>1.029835027825902</v>
       </c>
       <c r="E15">
-        <v>-21.74637730484975</v>
+        <v>-21.80021633232694</v>
       </c>
       <c r="F15">
-        <v>0.8493368781560577</v>
+        <v>0.3036520005204108</v>
       </c>
       <c r="G15">
-        <v>-4.732253850688454</v>
+        <v>-3.448401116740313</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>2.264859715853988</v>
       </c>
       <c r="E16">
-        <v>-22.42880475238365</v>
+        <v>-21.12304191464194</v>
       </c>
       <c r="F16">
-        <v>0.8916344957456145</v>
+        <v>0.6899986422977794</v>
       </c>
       <c r="G16">
-        <v>-5.075580596929651</v>
+        <v>-2.71241056408616</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>3.402541589783215</v>
       </c>
       <c r="E17">
-        <v>-23.0304985653088</v>
+        <v>-23.38395954702949</v>
       </c>
       <c r="F17">
-        <v>1.109732972184442</v>
+        <v>0.7799990657662877</v>
       </c>
       <c r="G17">
-        <v>-4.382776110835291</v>
+        <v>-2.654734239700977</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>4.395329913349662</v>
       </c>
       <c r="E18">
-        <v>-23.64777485729435</v>
+        <v>-22.92288390899052</v>
       </c>
       <c r="F18">
-        <v>1.10276783356834</v>
+        <v>0.6725351171682287</v>
       </c>
       <c r="G18">
-        <v>-4.530764117531792</v>
+        <v>-2.664566559952613</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>5.194221822797579</v>
       </c>
       <c r="E19">
-        <v>-25.04475474697256</v>
+        <v>-23.65934510838395</v>
       </c>
       <c r="F19">
-        <v>1.339547704985692</v>
+        <v>1.215356654508761</v>
       </c>
       <c r="G19">
-        <v>-3.437006218994141</v>
+        <v>-1.335475221210331</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>5.754710927279164</v>
       </c>
       <c r="E20">
-        <v>-25.48371784643208</v>
+        <v>-24.00799232223449</v>
       </c>
       <c r="F20">
-        <v>1.374189688180014</v>
+        <v>0.9604322644182195</v>
       </c>
       <c r="G20">
-        <v>-3.513724801321211</v>
+        <v>-1.787119706950942</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>6.047478557093767</v>
       </c>
       <c r="E21">
-        <v>-26.18751969128218</v>
+        <v>-25.33745266445833</v>
       </c>
       <c r="F21">
-        <v>1.465968613391561</v>
+        <v>0.7395955604515966</v>
       </c>
       <c r="G21">
-        <v>-3.53462758585617</v>
+        <v>-1.750822885658373</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>6.063439698573724</v>
       </c>
       <c r="E22">
-        <v>-25.83988685560936</v>
+        <v>-26.0229277749994</v>
       </c>
       <c r="F22">
-        <v>1.607238348460591</v>
+        <v>0.6200843609547896</v>
       </c>
       <c r="G22">
-        <v>-3.346896479960718</v>
+        <v>-0.9883016210525006</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>5.817289327509933</v>
       </c>
       <c r="E23">
-        <v>-26.22862917832381</v>
+        <v>-25.78020609666227</v>
       </c>
       <c r="F23">
-        <v>1.214024757833877</v>
+        <v>0.6644756377645573</v>
       </c>
       <c r="G23">
-        <v>-3.300290619858859</v>
+        <v>-2.105395555096474</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>5.34635757103963</v>
       </c>
       <c r="E24">
-        <v>-26.10893708182708</v>
+        <v>-27.136162540305</v>
       </c>
       <c r="F24">
-        <v>1.47450478827578</v>
+        <v>0.7280060005624107</v>
       </c>
       <c r="G24">
-        <v>-3.608982438668201</v>
+        <v>-1.971460814214179</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>4.705383248154869</v>
       </c>
       <c r="E25">
-        <v>-26.81904709096987</v>
+        <v>-26.0794295451931</v>
       </c>
       <c r="F25">
-        <v>1.254901791217284</v>
+        <v>0.5534443915919708</v>
       </c>
       <c r="G25">
-        <v>-3.36142646433258</v>
+        <v>-2.189801224165732</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>3.959372856559472</v>
       </c>
       <c r="E26">
-        <v>-26.58171882517588</v>
+        <v>-28.21935993751773</v>
       </c>
       <c r="F26">
-        <v>1.322361328391343</v>
+        <v>0.6872635821818155</v>
       </c>
       <c r="G26">
-        <v>-3.63774114776785</v>
+        <v>-0.9713814228012856</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>3.175941217342896</v>
       </c>
       <c r="E27">
-        <v>-26.98430469293178</v>
+        <v>-24.87824275771052</v>
       </c>
       <c r="F27">
-        <v>1.367243554034897</v>
+        <v>0.8203708969626702</v>
       </c>
       <c r="G27">
-        <v>-3.504591006178362</v>
+        <v>-1.509984008221933</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>2.416124484015943</v>
       </c>
       <c r="E28">
-        <v>-26.67308078828063</v>
+        <v>-26.4363185817376</v>
       </c>
       <c r="F28">
-        <v>1.125386321452646</v>
+        <v>0.3367989653305584</v>
       </c>
       <c r="G28">
-        <v>-3.240356503415893</v>
+        <v>-2.55152136142312</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>1.726953106458643</v>
       </c>
       <c r="E29">
-        <v>-27.43848346505707</v>
+        <v>-26.46736579953419</v>
       </c>
       <c r="F29">
-        <v>1.254930297923762</v>
+        <v>0.4348549089379495</v>
       </c>
       <c r="G29">
-        <v>-3.248970542909077</v>
+        <v>-1.946254320478168</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>1.136858622636626</v>
       </c>
       <c r="E30">
-        <v>-25.91275905934079</v>
+        <v>-26.21396597948698</v>
       </c>
       <c r="F30">
-        <v>1.382493058294663</v>
+        <v>0.1429636553692204</v>
       </c>
       <c r="G30">
-        <v>-3.398368842005307</v>
+        <v>-1.084618632972057</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>0.6608613296998509</v>
       </c>
       <c r="E31">
-        <v>-26.80588281702957</v>
+        <v>-26.00364100420073</v>
       </c>
       <c r="F31">
-        <v>1.363008724417011</v>
+        <v>0.03779845590742164</v>
       </c>
       <c r="G31">
-        <v>-3.436539432073104</v>
+        <v>-1.776085658668551</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>0.2947374899562045</v>
       </c>
       <c r="E32">
-        <v>-26.96687912495027</v>
+        <v>-25.30201735534831</v>
       </c>
       <c r="F32">
-        <v>1.104744298550808</v>
+        <v>0.5737609629281858</v>
       </c>
       <c r="G32">
-        <v>-3.946850095315139</v>
+        <v>-0.7110566743206959</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>0.02198661496602341</v>
       </c>
       <c r="E33">
-        <v>-24.96630346326368</v>
+        <v>-25.29442763291146</v>
       </c>
       <c r="F33">
-        <v>0.9386911496110667</v>
+        <v>0.6275056068745388</v>
       </c>
       <c r="G33">
-        <v>-3.78450094206928</v>
+        <v>-1.351981601269137</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.1846191226347132</v>
       </c>
       <c r="E34">
-        <v>-25.2160488047867</v>
+        <v>-25.47806631087051</v>
       </c>
       <c r="F34">
-        <v>1.210958703181586</v>
+        <v>0.360871295245238</v>
       </c>
       <c r="G34">
-        <v>-4.036218272147766</v>
+        <v>-1.793171384196729</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.3525456969828936</v>
       </c>
       <c r="E35">
-        <v>-24.87575662548031</v>
+        <v>-24.65389309842251</v>
       </c>
       <c r="F35">
-        <v>1.217803480148115</v>
+        <v>0.5994803469949224</v>
       </c>
       <c r="G35">
-        <v>-3.817910967651605</v>
+        <v>-1.349326543746642</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.509205747756177</v>
       </c>
       <c r="E36">
-        <v>-23.72250826384293</v>
+        <v>-25.59107437973192</v>
       </c>
       <c r="F36">
-        <v>1.340146345821728</v>
+        <v>0.6496505666901287</v>
       </c>
       <c r="G36">
-        <v>-3.599547383881278</v>
+        <v>-1.600242721804622</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.6743195247966856</v>
       </c>
       <c r="E37">
-        <v>-24.50181335582292</v>
+        <v>-23.61785070105166</v>
       </c>
       <c r="F37">
-        <v>1.483584174288994</v>
+        <v>0.8179430757943015</v>
       </c>
       <c r="G37">
-        <v>-3.705484841137956</v>
+        <v>-1.975466574316697</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.8577895314416734</v>
       </c>
       <c r="E38">
-        <v>-24.17779198362609</v>
+        <v>-24.05963503981796</v>
       </c>
       <c r="F38">
-        <v>1.530607570330222</v>
+        <v>0.8231693053152517</v>
       </c>
       <c r="G38">
-        <v>-3.338414862289106</v>
+        <v>-1.137196717226762</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-1.058177745833941</v>
       </c>
       <c r="E39">
-        <v>-23.34084847447647</v>
+        <v>-23.20937781708579</v>
       </c>
       <c r="F39">
-        <v>1.592741104510658</v>
+        <v>1.012772161217578</v>
       </c>
       <c r="G39">
-        <v>-3.300025776215717</v>
+        <v>-1.972669163336013</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.268629521275652</v>
       </c>
       <c r="E40">
-        <v>-22.79647608554041</v>
+        <v>-22.10750952153943</v>
       </c>
       <c r="F40">
-        <v>1.748012383578088</v>
+        <v>1.537005742228597</v>
       </c>
       <c r="G40">
-        <v>-3.833861176059814</v>
+        <v>-2.220317832946733</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-1.479709396634432</v>
       </c>
       <c r="E41">
-        <v>-22.99127292345436</v>
+        <v>-21.82041785487516</v>
       </c>
       <c r="F41">
-        <v>1.699709353157185</v>
+        <v>1.263544074397837</v>
       </c>
       <c r="G41">
-        <v>-3.627630741690915</v>
+        <v>-2.370931102255876</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-1.683142518923157</v>
       </c>
       <c r="E42">
-        <v>-21.65317225282388</v>
+        <v>-20.93886434827598</v>
       </c>
       <c r="F42">
-        <v>2.056519879611607</v>
+        <v>1.471951854340091</v>
       </c>
       <c r="G42">
-        <v>-3.447970745820207</v>
+        <v>-2.96164829555573</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.873970577717794</v>
       </c>
       <c r="E43">
-        <v>-21.81455348103523</v>
+        <v>-21.00268866094008</v>
       </c>
       <c r="F43">
-        <v>2.004056453750845</v>
+        <v>1.344697916622701</v>
       </c>
       <c r="G43">
-        <v>-4.633066595786349</v>
+        <v>-3.022618612752488</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.053816748493824</v>
       </c>
       <c r="E44">
-        <v>-21.24277929587875</v>
+        <v>-19.3424142355079</v>
       </c>
       <c r="F44">
-        <v>1.982776197365085</v>
+        <v>1.528281106340441</v>
       </c>
       <c r="G44">
-        <v>-4.852817298137632</v>
+        <v>-3.15946994425488</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.229370937168056</v>
       </c>
       <c r="E45">
-        <v>-19.80691792837068</v>
+        <v>-19.75382609910475</v>
       </c>
       <c r="F45">
-        <v>1.997721630089087</v>
+        <v>1.328444342812546</v>
       </c>
       <c r="G45">
-        <v>-4.885250712785871</v>
+        <v>-3.338471141563273</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.408649522671413</v>
       </c>
       <c r="E46">
-        <v>-20.34775357910675</v>
+        <v>-18.50370009302128</v>
       </c>
       <c r="F46">
-        <v>1.871961127049956</v>
+        <v>1.643807701754003</v>
       </c>
       <c r="G46">
-        <v>-4.609459095545807</v>
+        <v>-3.289150634119211</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.5987978344943</v>
       </c>
       <c r="E47">
-        <v>-19.81445330911944</v>
+        <v>-18.88402851102948</v>
       </c>
       <c r="F47">
-        <v>2.121049560842103</v>
+        <v>1.66466510866034</v>
       </c>
       <c r="G47">
-        <v>-5.57351975149143</v>
+        <v>-4.086902724354007</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.805738698342917</v>
       </c>
       <c r="E48">
-        <v>-19.70671185552895</v>
+        <v>-17.68468481246803</v>
       </c>
       <c r="F48">
-        <v>2.037328531328312</v>
+        <v>2.008112324600285</v>
       </c>
       <c r="G48">
-        <v>-5.730605137329848</v>
+        <v>-4.374469952077259</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.033934900753455</v>
       </c>
       <c r="E49">
-        <v>-17.92127946547277</v>
+        <v>-17.60021065832894</v>
       </c>
       <c r="F49">
-        <v>2.047397733538676</v>
+        <v>1.857177232329329</v>
       </c>
       <c r="G49">
-        <v>-5.939166195758394</v>
+        <v>-4.917581500522394</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.283469188382703</v>
       </c>
       <c r="E50">
-        <v>-18.52670021250624</v>
+        <v>-17.35866185475981</v>
       </c>
       <c r="F50">
-        <v>2.165192195823147</v>
+        <v>1.572113334962059</v>
       </c>
       <c r="G50">
-        <v>-5.837711217161888</v>
+        <v>-5.041263481869565</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.552742462514007</v>
       </c>
       <c r="E51">
-        <v>-17.92048698252143</v>
+        <v>-16.56470262089099</v>
       </c>
       <c r="F51">
-        <v>2.090409602496096</v>
+        <v>1.962772407947169</v>
       </c>
       <c r="G51">
-        <v>-6.433162490582901</v>
+        <v>-5.114449712106234</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.839340749062051</v>
       </c>
       <c r="E52">
-        <v>-17.01643601705214</v>
+        <v>-16.08695767002979</v>
       </c>
       <c r="F52">
-        <v>2.245052150315096</v>
+        <v>2.214700426445699</v>
       </c>
       <c r="G52">
-        <v>-6.232712268725569</v>
+        <v>-5.428838979788662</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.144412130845945</v>
       </c>
       <c r="E53">
-        <v>-16.44720683428798</v>
+        <v>-15.94124496188498</v>
       </c>
       <c r="F53">
-        <v>2.270171309839881</v>
+        <v>2.004930659416167</v>
       </c>
       <c r="G53">
-        <v>-6.553739180214236</v>
+        <v>-5.875908291594</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.467662055141099</v>
       </c>
       <c r="E54">
-        <v>-16.14909286188903</v>
+        <v>-15.42263959005256</v>
       </c>
       <c r="F54">
-        <v>2.237565972452814</v>
+        <v>1.854651221394203</v>
       </c>
       <c r="G54">
-        <v>-6.713608734851181</v>
+        <v>-6.452251096162338</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.809467621354655</v>
       </c>
       <c r="E55">
-        <v>-16.60194026265607</v>
+        <v>-14.3261964063674</v>
       </c>
       <c r="F55">
-        <v>1.897208566753892</v>
+        <v>2.095361850893675</v>
       </c>
       <c r="G55">
-        <v>-6.504726553505326</v>
+        <v>-6.600835001055907</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.169467284634056</v>
       </c>
       <c r="E56">
-        <v>-16.45710607846875</v>
+        <v>-14.19103051418645</v>
       </c>
       <c r="F56">
-        <v>2.209737092106712</v>
+        <v>2.122674443111344</v>
       </c>
       <c r="G56">
-        <v>-7.427604022942416</v>
+        <v>-6.448400931700165</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.549093487773098</v>
       </c>
       <c r="E57">
-        <v>-15.26596344633518</v>
+        <v>-13.99817186314779</v>
       </c>
       <c r="F57">
-        <v>2.175256646915765</v>
+        <v>2.10592041823191</v>
       </c>
       <c r="G57">
-        <v>-7.039426005735172</v>
+        <v>-6.158380589732314</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.944552652493998</v>
       </c>
       <c r="E58">
-        <v>-15.03831252949559</v>
+        <v>-13.67461692377375</v>
       </c>
       <c r="F58">
-        <v>2.253772035085506</v>
+        <v>1.907800391916351</v>
       </c>
       <c r="G58">
-        <v>-7.507954273726066</v>
+        <v>-6.910519983527031</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.348297597694274</v>
       </c>
       <c r="E59">
-        <v>-14.80863738477456</v>
+        <v>-11.29538385098779</v>
       </c>
       <c r="F59">
-        <v>2.2709219864438</v>
+        <v>1.924519575265645</v>
       </c>
       <c r="G59">
-        <v>-7.445653117222522</v>
+        <v>-7.37439031394417</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.75080667741422</v>
       </c>
       <c r="E60">
-        <v>-14.14900627539527</v>
+        <v>-13.41101445178726</v>
       </c>
       <c r="F60">
-        <v>2.140972581258331</v>
+        <v>2.266159782756073</v>
       </c>
       <c r="G60">
-        <v>-7.96594507526546</v>
+        <v>-7.024194185708986</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.144949952674732</v>
       </c>
       <c r="E61">
-        <v>-14.58540625856645</v>
+        <v>-13.04608284540513</v>
       </c>
       <c r="F61">
-        <v>2.204932128359269</v>
+        <v>1.874401617865648</v>
       </c>
       <c r="G61">
-        <v>-8.208177692373933</v>
+        <v>-7.65401885346425</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.522666098602262</v>
       </c>
       <c r="E62">
-        <v>-15.22248556738754</v>
+        <v>-14.41018601378766</v>
       </c>
       <c r="F62">
-        <v>2.445504975444098</v>
+        <v>2.224923248129861</v>
       </c>
       <c r="G62">
-        <v>-7.829788958326315</v>
+        <v>-8.288110814419635</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.874733872389165</v>
       </c>
       <c r="E63">
-        <v>-13.94123988792336</v>
+        <v>-11.8767448156185</v>
       </c>
       <c r="F63">
-        <v>1.882290057030452</v>
+        <v>2.011181546664407</v>
       </c>
       <c r="G63">
-        <v>-7.985881180502951</v>
+        <v>-8.217533294067913</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.191950276681391</v>
       </c>
       <c r="E64">
-        <v>-14.01341923513161</v>
+        <v>-12.04973705118552</v>
       </c>
       <c r="F64">
-        <v>1.997232264961216</v>
+        <v>2.264495307838946</v>
       </c>
       <c r="G64">
-        <v>-8.303359187173518</v>
+        <v>-8.069992211019214</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.470639245199957</v>
       </c>
       <c r="E65">
-        <v>-13.40102010965233</v>
+        <v>-11.43190375689703</v>
       </c>
       <c r="F65">
-        <v>2.096923384926299</v>
+        <v>2.063329815047997</v>
       </c>
       <c r="G65">
-        <v>-8.312926663782013</v>
+        <v>-8.539579853582675</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.709445257545667</v>
       </c>
       <c r="E66">
-        <v>-14.3751401534423</v>
+        <v>-11.3198330821552</v>
       </c>
       <c r="F66">
-        <v>1.879230337201823</v>
+        <v>1.855013890048838</v>
       </c>
       <c r="G66">
-        <v>-7.848536577715207</v>
+        <v>-8.669028805259257</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.906078375952342</v>
       </c>
       <c r="E67">
-        <v>-13.52434857077722</v>
+        <v>-11.37892513948129</v>
       </c>
       <c r="F67">
-        <v>1.778627002629448</v>
+        <v>1.856572256669631</v>
       </c>
       <c r="G67">
-        <v>-8.669035426350336</v>
+        <v>-8.8994990540667</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.060486746113872</v>
       </c>
       <c r="E68">
-        <v>-13.31001136752018</v>
+        <v>-10.818476667818</v>
       </c>
       <c r="F68">
-        <v>1.980723714498675</v>
+        <v>2.150348120277733</v>
       </c>
       <c r="G68">
-        <v>-9.021615147373796</v>
+        <v>-8.86570500520182</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.175028827427937</v>
       </c>
       <c r="E69">
-        <v>-13.90936395938337</v>
+        <v>-10.71139184295862</v>
       </c>
       <c r="F69">
-        <v>1.972174869967133</v>
+        <v>1.761233160560176</v>
       </c>
       <c r="G69">
-        <v>-8.70594469856767</v>
+        <v>-8.485247180192156</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.254935036037239</v>
       </c>
       <c r="E70">
-        <v>-14.18685978962539</v>
+        <v>-10.39827050769825</v>
       </c>
       <c r="F70">
-        <v>1.989411925150776</v>
+        <v>1.518576156490629</v>
       </c>
       <c r="G70">
-        <v>-9.024538359084971</v>
+        <v>-8.822985725563063</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.302246945128278</v>
       </c>
       <c r="E71">
-        <v>-13.51164620118571</v>
+        <v>-11.31312641214984</v>
       </c>
       <c r="F71">
-        <v>1.692836069484177</v>
+        <v>2.258049624763108</v>
       </c>
       <c r="G71">
-        <v>-9.177528600091311</v>
+        <v>-9.103253200372222</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.314898215450055</v>
       </c>
       <c r="E72">
-        <v>-14.63494776421036</v>
+        <v>-11.86954454194631</v>
       </c>
       <c r="F72">
-        <v>1.960700920609775</v>
+        <v>2.238710991829677</v>
       </c>
       <c r="G72">
-        <v>-9.227147056633909</v>
+        <v>-8.601457260257193</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.292281234952645</v>
       </c>
       <c r="E73">
-        <v>-13.7789665503325</v>
+        <v>-11.61544280842791</v>
       </c>
       <c r="F73">
-        <v>1.937722931482664</v>
+        <v>2.046368324693641</v>
       </c>
       <c r="G73">
-        <v>-8.613206386376067</v>
+        <v>-9.089461467655619</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.237574562355514</v>
       </c>
       <c r="E74">
-        <v>-14.53487301711486</v>
+        <v>-11.33294301440741</v>
       </c>
       <c r="F74">
-        <v>1.552887145148624</v>
+        <v>1.275564402296022</v>
       </c>
       <c r="G74">
-        <v>-9.665767856223026</v>
+        <v>-9.530869746588804</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-9.152990962698723</v>
       </c>
       <c r="E75">
-        <v>-14.12008744038229</v>
+        <v>-11.783757130345</v>
       </c>
       <c r="F75">
-        <v>1.764799666281746</v>
+        <v>1.672118028698398</v>
       </c>
       <c r="G75">
-        <v>-9.788426878998562</v>
+        <v>-8.968288879827215</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-9.04007153416903</v>
       </c>
       <c r="E76">
-        <v>-14.77676145623457</v>
+        <v>-11.24869981244272</v>
       </c>
       <c r="F76">
-        <v>1.407963800532676</v>
+        <v>1.602287683768927</v>
       </c>
       <c r="G76">
-        <v>-9.578852793635001</v>
+        <v>-9.133548002602094</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-8.904485796402962</v>
       </c>
       <c r="E77">
-        <v>-14.93106015109792</v>
+        <v>-12.75851568897005</v>
       </c>
       <c r="F77">
-        <v>1.28370148328955</v>
+        <v>1.41068143988357</v>
       </c>
       <c r="G77">
-        <v>-9.536252693635658</v>
+        <v>-8.876206055652387</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-8.754972964956991</v>
       </c>
       <c r="E78">
-        <v>-15.29097873675355</v>
+        <v>-13.20988227873658</v>
       </c>
       <c r="F78">
-        <v>1.551601175945287</v>
+        <v>1.420837745919283</v>
       </c>
       <c r="G78">
-        <v>-9.193445703044127</v>
+        <v>-9.686723609486613</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-8.597890604190972</v>
       </c>
       <c r="E79">
-        <v>-16.14427003707086</v>
+        <v>-13.22644290818263</v>
       </c>
       <c r="F79">
-        <v>1.564209058738101</v>
+        <v>1.28063542863726</v>
       </c>
       <c r="G79">
-        <v>-9.159453021446891</v>
+        <v>-8.071442229965415</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-8.436224446047857</v>
       </c>
       <c r="E80">
-        <v>-16.48421805235267</v>
+        <v>-13.6053946700925</v>
       </c>
       <c r="F80">
-        <v>1.485915389396521</v>
+        <v>1.609027936145037</v>
       </c>
       <c r="G80">
-        <v>-9.951252750802077</v>
+        <v>-8.098287443743365</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-8.272552797050773</v>
       </c>
       <c r="E81">
-        <v>-17.09130527782096</v>
+        <v>-14.30119922984506</v>
       </c>
       <c r="F81">
-        <v>1.524483379555218</v>
+        <v>1.287226812657319</v>
       </c>
       <c r="G81">
-        <v>-8.956559616981577</v>
+        <v>-8.198322198303522</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-8.110343050227968</v>
       </c>
       <c r="E82">
-        <v>-17.03173320225006</v>
+        <v>-15.10579132068388</v>
       </c>
       <c r="F82">
-        <v>1.236161799119889</v>
+        <v>1.481131013825978</v>
       </c>
       <c r="G82">
-        <v>-8.835165222602042</v>
+        <v>-8.96386268044121</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-7.949748983189458</v>
       </c>
       <c r="E83">
-        <v>-17.4822846666952</v>
+        <v>-15.62614015500925</v>
       </c>
       <c r="F83">
-        <v>1.547480373153314</v>
+        <v>1.307170421250448</v>
       </c>
       <c r="G83">
-        <v>-8.690716189087022</v>
+        <v>-8.513380196184883</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-7.787413823669818</v>
       </c>
       <c r="E84">
-        <v>-18.22780281410396</v>
+        <v>-16.68984247161896</v>
       </c>
       <c r="F84">
-        <v>1.534161406404468</v>
+        <v>1.380142838716151</v>
       </c>
       <c r="G84">
-        <v>-9.092722355011801</v>
+        <v>-7.958966445268676</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-7.618639877603499</v>
       </c>
       <c r="E85">
-        <v>-20.19251749012381</v>
+        <v>-16.586547979504</v>
       </c>
       <c r="F85">
-        <v>1.226520197506694</v>
+        <v>1.522666868870209</v>
       </c>
       <c r="G85">
-        <v>-8.820466400407678</v>
+        <v>-8.197670020832286</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-7.441779023269269</v>
       </c>
       <c r="E86">
-        <v>-21.64632067165027</v>
+        <v>-18.67357673847102</v>
       </c>
       <c r="F86">
-        <v>1.513886803275012</v>
+        <v>1.007758148289297</v>
       </c>
       <c r="G86">
-        <v>-8.195157316767979</v>
+        <v>-7.215507301877929</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.255839811647267</v>
       </c>
       <c r="E87">
-        <v>-21.86034993867479</v>
+        <v>-19.39782011499175</v>
       </c>
       <c r="F87">
-        <v>1.252792294937919</v>
+        <v>1.296920676565724</v>
       </c>
       <c r="G87">
-        <v>-8.42127088764574</v>
+        <v>-8.105948046121238</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-7.060178984849249</v>
       </c>
       <c r="E88">
-        <v>-23.00746674650579</v>
+        <v>-19.81247436597809</v>
       </c>
       <c r="F88">
-        <v>1.294402584160175</v>
+        <v>1.016107445875493</v>
       </c>
       <c r="G88">
-        <v>-7.784666222626049</v>
+        <v>-7.370871204035925</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.855110323883825</v>
       </c>
       <c r="E89">
-        <v>-24.52672901981312</v>
+        <v>-24.24948225564152</v>
       </c>
       <c r="F89">
-        <v>1.386529924673118</v>
+        <v>1.09379455585146</v>
       </c>
       <c r="G89">
-        <v>-8.486968663872577</v>
+        <v>-6.40105019885197</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-6.646042847247958</v>
       </c>
       <c r="E90">
-        <v>-25.20916099582103</v>
+        <v>-23.17900987039035</v>
       </c>
       <c r="F90">
-        <v>1.645876021679567</v>
+        <v>1.528993774002389</v>
       </c>
       <c r="G90">
-        <v>-7.752683042171149</v>
+        <v>-6.976019127021512</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-6.438873683054491</v>
       </c>
       <c r="E91">
-        <v>-29.1337901654126</v>
+        <v>-25.53097247270212</v>
       </c>
       <c r="F91">
-        <v>1.259562637726422</v>
+        <v>1.714380804757816</v>
       </c>
       <c r="G91">
-        <v>-7.965955006902078</v>
+        <v>-6.521090580105943</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.238179002330519</v>
       </c>
       <c r="E92">
-        <v>-28.85952313713804</v>
+        <v>-26.96554775359201</v>
       </c>
       <c r="F92">
-        <v>1.174576227186195</v>
+        <v>1.389909553096666</v>
       </c>
       <c r="G92">
-        <v>-7.238108396274533</v>
+        <v>-6.130204536647576</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.046868505398423</v>
       </c>
       <c r="E93">
-        <v>-30.86366270786866</v>
+        <v>-29.41447856983002</v>
       </c>
       <c r="F93">
-        <v>1.014374871604002</v>
+        <v>1.229212497562941</v>
       </c>
       <c r="G93">
-        <v>-7.273620618274294</v>
+        <v>-6.02285016590009</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-5.870773501955767</v>
       </c>
       <c r="E94">
-        <v>-33.15725554445856</v>
+        <v>-31.46846984667409</v>
       </c>
       <c r="F94">
-        <v>0.8854390382044153</v>
+        <v>1.398849572989322</v>
       </c>
       <c r="G94">
-        <v>-7.293450786054529</v>
+        <v>-6.475150139657477</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.714693977033419</v>
       </c>
       <c r="E95">
-        <v>-35.57383947085979</v>
+        <v>-34.54247951561287</v>
       </c>
       <c r="F95">
-        <v>0.9841672649729105</v>
+        <v>1.122936328401461</v>
       </c>
       <c r="G95">
-        <v>-7.058315978582254</v>
+        <v>-5.991360256730543</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.578176567567519</v>
       </c>
       <c r="E96">
-        <v>-37.91199022744816</v>
+        <v>-36.1692522903363</v>
       </c>
       <c r="F96">
-        <v>1.050212552764482</v>
+        <v>0.9375809717643437</v>
       </c>
       <c r="G96">
-        <v>-7.141854284720223</v>
+        <v>-6.559241306900504</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.455472484311146</v>
       </c>
       <c r="E97">
-        <v>-39.73795472410999</v>
+        <v>-37.85577375111694</v>
       </c>
       <c r="F97">
-        <v>0.7216094123699508</v>
+        <v>1.069465665578479</v>
       </c>
       <c r="G97">
-        <v>-7.494632638476039</v>
+        <v>-6.679831238713997</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.338733379287253</v>
       </c>
       <c r="E98">
-        <v>-42.12758517321756</v>
+        <v>-39.55155820548028</v>
       </c>
       <c r="F98">
-        <v>0.5066363795552425</v>
+        <v>0.6963223800181292</v>
       </c>
       <c r="G98">
-        <v>-6.895394100958101</v>
+        <v>-6.263573174242655</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.221619793363833</v>
       </c>
       <c r="E99">
-        <v>-44.35883677238087</v>
+        <v>-44.00588750822305</v>
       </c>
       <c r="F99">
-        <v>0.4620146735347783</v>
+        <v>0.6714882875581232</v>
       </c>
       <c r="G99">
-        <v>-7.377386357657211</v>
+        <v>-5.834016648340062</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.095325961162566</v>
       </c>
       <c r="E100">
-        <v>-47.21888510140524</v>
+        <v>-44.552560361955</v>
       </c>
       <c r="F100">
-        <v>0.4992673959307027</v>
+        <v>0.6446761464097334</v>
       </c>
       <c r="G100">
-        <v>-7.409260290109314</v>
+        <v>-6.860494329883104</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.957705130316379</v>
       </c>
       <c r="E101">
-        <v>-49.0548450723205</v>
+        <v>-48.01798188903575</v>
       </c>
       <c r="F101">
-        <v>0.1749782704498289</v>
+        <v>0.1776270185934013</v>
       </c>
       <c r="G101">
-        <v>-6.33173399635071</v>
+        <v>-6.075196511967047</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.80623439925154</v>
       </c>
       <c r="E102">
-        <v>-51.11538905105366</v>
+        <v>-50.80260961558088</v>
       </c>
       <c r="F102">
-        <v>0.3508781109188151</v>
+        <v>-0.08450798453013601</v>
       </c>
       <c r="G102">
-        <v>-7.193478931859618</v>
+        <v>-6.472620882865474</v>
       </c>
     </row>
   </sheetData>
